--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129164295</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>56916</v>
+        <v>56918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>129165099</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,6 +1047,226 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129278511</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58095</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Liamyren sydväst, Sönder Össjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>402744</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6251503</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skånes-Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt Arne Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt Arne Johansson, Björn Herrlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129278569</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58442</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Liamyren sydväst, Sönder Össjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>402744</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6251503</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skånes-Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt Arne Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt Arne Johansson, Björn Herrlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129164295</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>56918</v>
+        <v>56920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>129165099</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129278511</v>
       </c>
       <c r="B5" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>129278569</v>
       </c>
       <c r="B6" t="n">
-        <v>58442</v>
+        <v>58444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129164295</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>56920</v>
+        <v>56923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>129165099</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129278511</v>
       </c>
       <c r="B5" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>129278569</v>
       </c>
       <c r="B6" t="n">
-        <v>58444</v>
+        <v>58447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>129278511</v>
       </c>
       <c r="B5" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>129278569</v>
       </c>
       <c r="B6" t="n">
-        <v>58447</v>
+        <v>58452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>129278511</v>
       </c>
       <c r="B5" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>129278569</v>
       </c>
       <c r="B6" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>56923</v>
+        <v>57096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>57096</v>
+        <v>57098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>57098</v>
+        <v>57103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>57103</v>
+        <v>57105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>57139</v>
+        <v>57140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>57140</v>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -675,48 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129164295</v>
+        <v>129165099</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -761,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kanske fler.</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +797,7 @@
         <v>129165390</v>
       </c>
       <c r="B3" t="n">
-        <v>57144</v>
+        <v>57165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,27 +922,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165099</v>
+        <v>129278511</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,16 +950,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1008,22 +995,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,47 +1020,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt Arne Johansson</t>
+          <t>Kurt Arne Johansson, Björn Herrlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129278511</v>
+        <v>129164295</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1123,12 +1108,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kanske fler.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kurt Arne Johansson, Björn Herrlund</t>
+          <t>Kurt Arne Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
         <v>129278569</v>
       </c>
       <c r="B6" t="n">
-        <v>58453</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129165390</v>
+        <v>134710540</v>
       </c>
       <c r="B3" t="n">
-        <v>57165</v>
+        <v>57776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,37 +805,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102118</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -875,27 +875,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hördes från myren</t>
+          <t>Fint spel med vingklapper.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129278511</v>
+        <v>129165390</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>57165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,12 +950,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -995,12 +1003,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hördes från myren</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,55 +1043,47 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt Arne Johansson, Björn Herrlund</t>
+          <t>Kurt Arne Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129164295</v>
+        <v>129278511</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1108,27 +1123,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kanske fler.</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kurt Arne Johansson</t>
+          <t>Kurt Arne Johansson, Björn Herrlund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129278569</v>
+        <v>129164295</v>
       </c>
       <c r="B6" t="n">
-        <v>58676</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,29 +1166,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1228,22 +1236,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kanske fler.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1276,125 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Kurt Arne Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129278569</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Liamyren sydväst, Sönder Össjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>402744</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6251503</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skånes-Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kurt Arne Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Kurt Arne Johansson, Björn Herrlund</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44382-2025 artfynd.xlsx
+++ b/artfynd/A 44382-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129165099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134710540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129165390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129278511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1280,6 +1305,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129164295</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,8 +1425,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129278569</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>